--- a/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VS_CEA_8C\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52DC527E-A33E-4BE7-AFD6-58FCE851F718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85024192-EADD-4F7C-9A08-A075838AEBEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" firstSheet="3" activeTab="8" xr2:uid="{58726868-4D11-4030-B78E-89DE76DCDDC6}"/>
+    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="12772" firstSheet="3" activeTab="8" xr2:uid="{CA2E4027-7266-4221-A6F2-47216B7E2B21}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links_FRA" sheetId="2" r:id="rId1"/>
@@ -4060,7 +4060,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B3E0D50-4CB1-429B-887E-202737193C50}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB7679C9-01CF-437F-92D3-CCCA1DFFB7C0}">
   <dimension ref="B3:R113"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7376,7 +7376,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BFF1C15-5832-4ED7-8BE9-E39246BF1893}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2986F862-7AC9-4748-BF14-6EF44A496D0D}">
   <dimension ref="B3:R95"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9360,7 +9360,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{326E47B6-B0E1-48F2-A6D8-D65DD6453B66}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D683872A-F36A-476B-A55E-0F6D8ACE7A17}">
   <dimension ref="B3:R35"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10153,7 +10153,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A95B2B-9EDC-410F-BC77-D4C246246240}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F21A5F5C-01B0-4A5F-8A17-BF95E37939F8}">
   <dimension ref="B3:R96"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -13231,7 +13231,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E7A4216-13E9-421D-BB08-B4F057A50FFF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EF69449-6464-4AEB-ACCF-59140941E613}">
   <dimension ref="B3:R43"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14811,7 +14811,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{169F2748-4FFA-4759-9934-A9B85D637527}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F16B7E46-DA2C-4B29-B770-C38D3C1BC119}">
   <dimension ref="B3:R92"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17185,7 +17185,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F104A0DA-8BBE-4ACB-8B0A-78E1FD41FCA2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B29682C5-AEA7-44DA-8301-3F0515CD2938}">
   <dimension ref="B3:R91"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19140,7 +19140,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2D89C27-2B2B-47CB-96FE-9B6192930169}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E340F6E0-FB2C-4535-9422-C551C169AE5E}">
   <dimension ref="B3:R42"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -20193,7 +20193,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{039E1A5C-664E-44E8-9628-06F13E8EB780}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E951CE7A-7376-4195-9C2C-A77F64A6C498}">
   <dimension ref="B3:R60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
